--- a/Release-Notes.xlsx
+++ b/Release-Notes.xlsx
@@ -2353,7 +2353,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-06-16 11:43:19 UTC</t>
+          <t>2025-06-22 00:55:50 UTC</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/Release-Notes.xlsx
+++ b/Release-Notes.xlsx
@@ -2353,7 +2353,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-06-22 00:55:50 UTC</t>
+          <t>2025-06-29 00:57:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>

--- a/Release-Notes.xlsx
+++ b/Release-Notes.xlsx
@@ -2353,7 +2353,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-06-29 00:57:09 UTC</t>
+          <t>2025-07-06 00:56:23 UTC</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>

--- a/Release-Notes.xlsx
+++ b/Release-Notes.xlsx
@@ -2353,7 +2353,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-07-06 00:56:23 UTC</t>
+          <t>2025-07-13 00:58:03 UTC</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>

--- a/Release-Notes.xlsx
+++ b/Release-Notes.xlsx
@@ -2353,7 +2353,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-07-13 00:58:03 UTC</t>
+          <t>2025-07-20 00:59:15 UTC</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
